--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/06-ghost-kitchen-peak-and-event-checklists.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/06-ghost-kitchen-peak-and-event-checklists.xlsx
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F7" s="28" t="n"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F8" s="28" t="n"/>
